--- a/reports/二级子公司D_利润表_2025-10.xlsx
+++ b/reports/二级子公司D_利润表_2025-10.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>87555453</v>
+        <v>88802560</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>85630168</v>
+        <v>84964209</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>825008461</v>
+        <v>824088230</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>294759</v>
+        <v>295469</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>2844917</v>
+        <v>2845618</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>250934</v>
+        <v>253492</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2438320</v>
+        <v>2440196</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>211135</v>
+        <v>211218</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2032044</v>
+        <v>2034143</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>187873</v>
+        <v>189881</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1828787</v>
+        <v>1830971</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>105614</v>
+        <v>105284</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1015991</v>
+        <v>1017130</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>83574</v>
+        <v>84022</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>812817</v>
+        <v>813482</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>86421564</v>
+        <v>87663194</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>84496279</v>
+        <v>83824843</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>4724802</v>
+        <v>4698343</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>45717976</v>
+        <v>45694701</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>368246</v>
+        <v>365301</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>3556152</v>
+        <v>3552670</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>627615</v>
+        <v>626679</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>6095780</v>
+        <v>6088961</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>75986720</v>
+        <v>75325391</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>731538663</v>
+        <v>730664161</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1252609</v>
+        <v>1258294</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>12191853</v>
+        <v>12180061</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>422500</v>
+        <v>420488</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>4063989</v>
+        <v>4061495</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2088732</v>
+        <v>2107297</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>20320351</v>
+        <v>20317062</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>527190</v>
+        <v>527717</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>5079849</v>
+        <v>5081789</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1885263</v>
+        <v>1901274</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>18288713</v>
+        <v>18302398</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>40022</v>
+        <v>40228</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>399980</v>
+        <v>400487</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1139037</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>10985851</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>757812</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>7323143</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>57513663</v>
+        <v>61079582</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>51641999</v>
+        <v>51110978</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>50702297</v>
+        <v>50171409</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>487680815</v>
+        <v>487611981</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>939702</v>
+        <v>939569</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>9144122</v>
+        <v>9138409</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1878758</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>18270148</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>601714</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>5845318</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>376731</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>3653372</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>453136</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>4384994</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>340707</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>3290004</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>227649</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2194390</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>190009</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1829561</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>897840</v>
+        <v>897848</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>8636052</v>
+        <v>8643219</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>678547</v>
+        <v>686316</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>6604059</v>
+        <v>6611325</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>527596</v>
+        <v>527209</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>5079884</v>
+        <v>5086034</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>3975881</v>
+        <v>3998312</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>38609313</v>
+        <v>38648800</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>150260</v>
+        <v>157436</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1499938</v>
+        <v>1525126</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>320087</v>
+        <v>319095</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>3200141</v>
+        <v>3200735</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>359193</v>
+        <v>319095</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>3599848</v>
+        <v>3200735</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>40158</v>
+        <v>39767</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>400014</v>
+        <v>399681</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>161045</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1618138</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>329124</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>3196626</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>107668</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1078692</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>80944</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>809258</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>135245</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1349381</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>474391</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>4571949</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>72395</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>720434</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>54324</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>540551</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>90491</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>901132</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>63250</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>630804</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>45079</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>450480</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>35973</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>360241</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>26916</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>270044</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>28907901</v>
+        <v>27729482</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>33155457</v>
+        <v>30835491</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>187900</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1826887</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>44788</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>449416</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>70209</v>
+        <v>69805</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>700027</v>
+        <v>699170</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>28837692</v>
+        <v>27847577</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2513965</v>
+        <v>2505337</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>25000470</v>
+        <v>24990259</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>26323727</v>
+        <v>25342240</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>26323727</v>
+        <v>25342240</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>26323727</v>
+        <v>25342240</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>26323727</v>
+        <v>25342240</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>26323727</v>
+        <v>25342240</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
